--- a/data/2026 Guidance_Country Names and Groupings.xlsx
+++ b/data/2026 Guidance_Country Names and Groupings.xlsx
@@ -7374,10 +7374,10 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001AD45DB714643E4A8A8C58D3ECEF2B52" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e0377062c7993f79e0ee2fe840fd08d8">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0611ad7-5071-45af-a141-b2a079deb018" xmlns:ns3="7f64e6aa-b736-4f26-84cc-faf427629e48" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2869b255174fce0a927e36b6c0c9136f" ns2:_="" ns3:_="">
-    <xsd:import namespace="b0611ad7-5071-45af-a141-b2a079deb018"/>
-    <xsd:import namespace="7f64e6aa-b736-4f26-84cc-faf427629e48"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE999D9A6EB5694A9E61F56E0C65FA6E" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7e3fa9533e1523351dc1a8c45d523838">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d2f08301-3572-41d6-bf1e-19bd96c47c4f" xmlns:ns3="4c3d6b82-f9af-440b-a18a-3e1dc74d2270" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="07f2a39ac6620e5ae12889bba8cde6ca" ns2:_="" ns3:_="">
+    <xsd:import namespace="d2f08301-3572-41d6-bf1e-19bd96c47c4f"/>
+    <xsd:import namespace="4c3d6b82-f9af-440b-a18a-3e1dc74d2270"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -7386,10 +7386,15 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -7397,7 +7402,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b0611ad7-5071-45af-a141-b2a079deb018" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d2f08301-3572-41d6-bf1e-19bd96c47c4f" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -7410,47 +7415,64 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1103e67f-0598-4a90-8a4a-cec34b03bfa0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="16" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="19" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7f64e6aa-b736-4f26-84cc-faf427629e48" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4c3d6b82-f9af-440b-a18a-3e1dc74d2270" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="TaxCatchAll" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f05aecd8-fc53-422d-90b0-cfbb054cca51}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="4c3d6b82-f9af-440b-a18a-3e1dc74d2270">
       <xsd:complexType>
         <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
+          <xsd:extension base="dms:MultiChoiceLookup">
             <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
             </xsd:sequence>
           </xsd:extension>
         </xsd:complexContent>
       </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -7555,13 +7577,10 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <SharedWithUsers xmlns="7f64e6aa-b736-4f26-84cc-faf427629e48">
-      <UserInfo>
-        <DisplayName>Cecilia Calderon</DisplayName>
-        <AccountId>14</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
+    <TaxCatchAll xmlns="4c3d6b82-f9af-440b-a18a-3e1dc74d2270" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d2f08301-3572-41d6-bf1e-19bd96c47c4f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
 </file>
@@ -7575,22 +7594,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E66ED643-5F43-47CB-8288-3F0E93434226}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b0611ad7-5071-45af-a141-b2a079deb018"/>
-    <ds:schemaRef ds:uri="7f64e6aa-b736-4f26-84cc-faf427629e48"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24AFDA0A-DD23-4066-9B8C-990D641D15A6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
